--- a/countries/fr/1990-1994.xlsx
+++ b/countries/fr/1990-1994.xlsx
@@ -765,11 +765,6 @@
       <c r="O2" t="n">
         <v>11</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_FR_ECDC_AIDS_ANNUAL</t>
@@ -787,12 +782,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -803,11 +793,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -872,7 +857,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -907,113 +892,30 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1990-01-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1990-01</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_FR_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:FR:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1021,12 +923,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1037,11 +934,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1141,24 +1033,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
-        <v>21</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>31</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1177,12 +1064,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1193,11 +1075,6 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1262,7 +1139,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1297,113 +1174,30 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_FR_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:FR:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1411,12 +1205,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1427,11 +1216,6 @@
       <c r="AT5" t="n">
         <v>1</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1531,24 +1315,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1992-01</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="O6" t="n">
-        <v>31</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>110</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1567,12 +1346,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1583,11 +1357,6 @@
       <c r="AT6" t="n">
         <v>1</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1624,1020 +1393,6 @@
         </is>
       </c>
       <c r="BC6" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>D005</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>艾滋病</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1992-01</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>31</v>
-      </c>
-      <c r="O7" t="n">
-        <v>31</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:FR:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>D005</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>艾滋病</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1993-01-01</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1993-01</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>56</v>
-      </c>
-      <c r="O8" t="n">
-        <v>56</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>D005</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>艾滋病</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1993-01-01</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1993-01</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>56</v>
-      </c>
-      <c r="O9" t="n">
-        <v>56</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:FR:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>D005</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>艾滋病</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1994-01-01</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1994-01</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>110</v>
-      </c>
-      <c r="O10" t="n">
-        <v>110</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>D005</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>艾滋病</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1994-01-01</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1994-01</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>110</v>
-      </c>
-      <c r="O11" t="n">
-        <v>110</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:FR:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -2769,7 +1524,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2789,7 +1544,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2799,7 +1554,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/countries/fr/1990-1994.xlsx
+++ b/countries/fr/1990-1994.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>11</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_FR_ECDC_AIDS_ANNUAL</t>
@@ -782,7 +787,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -792,6 +802,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -857,7 +872,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -892,30 +907,113 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1990-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_FR_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -923,7 +1021,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -933,6 +1036,11 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1033,19 +1141,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1992-01</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1064,7 +1177,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1074,6 +1192,11 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1139,7 +1262,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1174,30 +1297,113 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1993-01</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_FR_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1205,7 +1411,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1215,6 +1426,11 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1315,19 +1531,24 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="O6" t="n">
-        <v>110</v>
+        <v>31</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1346,7 +1567,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1357,6 +1583,11 @@
       <c r="AT6" t="n">
         <v>1</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -1393,6 +1624,1020 @@
         </is>
       </c>
       <c r="BC6" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1992-01</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>31</v>
+      </c>
+      <c r="O7" t="n">
+        <v>31</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1993-01</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>56</v>
+      </c>
+      <c r="O8" t="n">
+        <v>56</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1993-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>56</v>
+      </c>
+      <c r="O9" t="n">
+        <v>56</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1994-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>110</v>
+      </c>
+      <c r="O10" t="n">
+        <v>110</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1994-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>110</v>
+      </c>
+      <c r="O11" t="n">
+        <v>110</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -1524,7 +2769,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1544,7 +2789,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1554,7 +2799,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
